--- a/data/trans_orig/P44A$endoscopia-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P44A$endoscopia-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5719</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13141</t>
+          <t>13060</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8319</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17165</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16254</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27904</t>
+          <t>28066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -845,62 +845,62 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7025</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6923</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>21,82%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6044</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>9,97%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>48,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6270</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10509</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12930</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20971</t>
+          <t>20173</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>58,17%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14223</t>
+          <t>14315</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17102</t>
+          <t>16845</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,57%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>17183</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30589</t>
+          <t>30448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>14810</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>26899</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36707</t>
+          <t>37366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54470</t>
+          <t>55364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>75,73%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>15086</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19679</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14637</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13499</t>
+          <t>12882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29655</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>13882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>17385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26425</t>
+          <t>26231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26852</t>
+          <t>27126</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>14305</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24577</t>
+          <t>25237</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34312</t>
+          <t>33825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49518</t>
+          <t>49214</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,38%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>8594</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>15357</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16842</t>
+          <t>17285</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>13069</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28377</t>
+          <t>29324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>47,3%</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16026</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15831</t>
+          <t>16636</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15111</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28745</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,31%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10433</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13817</t>
+          <t>13827</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>17124</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13560</t>
+          <t>12710</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13099</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26439</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,83%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22089</t>
+          <t>21782</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,81%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57249</t>
+          <t>55486</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77847</t>
+          <t>78290</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55232</t>
+          <t>55119</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76516</t>
+          <t>76255</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117916</t>
+          <t>117157</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>147087</t>
+          <t>147876</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12508</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>30662</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>16111</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19817</t>
+          <t>19570</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>40649</t>
+          <t>42080</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30546</t>
+          <t>31229</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53643</t>
+          <t>52413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24440</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45004</t>
+          <t>45114</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60545</t>
+          <t>60319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90964</t>
+          <t>89254</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>27833</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28103</t>
+          <t>27274</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50006</t>
+          <t>47331</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>41755</t>
+          <t>42263</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>70122</t>
+          <t>69254</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>20432</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>25632</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>67,77%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>15591</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15743</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14033</t>
+          <t>14717</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>38,91%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>20430</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35144</t>
+          <t>34600</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15742</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28496</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39169</t>
+          <t>40279</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59823</t>
+          <t>59663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,12%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>14066</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24367</t>
+          <t>24709</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21612</t>
+          <t>21059</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40406</t>
+          <t>40410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4039,12 +4039,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21120</t>
+          <t>21355</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15474</t>
+          <t>15868</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>14616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32359</t>
+          <t>32452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11782</t>
+          <t>12070</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24797</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12727</t>
+          <t>12774</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23553</t>
+          <t>23829</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26639</t>
+          <t>27676</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44699</t>
+          <t>45301</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>60,32%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>11900</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16238</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12181</t>
+          <t>11900</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25598</t>
+          <t>25720</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20942</t>
+          <t>20021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37573</t>
+          <t>37362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,75%</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20671</t>
+          <t>20826</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13707</t>
+          <t>13512</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>14232</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>29313</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>27433</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12404</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26830</t>
+          <t>26183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32505</t>
+          <t>32274</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50263</t>
+          <t>50415</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>19011</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9309</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23268</t>
+          <t>22706</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20897</t>
+          <t>21582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37448</t>
+          <t>37490</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16009</t>
+          <t>14293</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>8165</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23047</t>
+          <t>23402</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69928</t>
+          <t>69918</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95964</t>
+          <t>94738</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52283</t>
+          <t>53034</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76630</t>
+          <t>75580</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>131253</t>
+          <t>131008</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165398</t>
+          <t>166096</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,22%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>25970</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15993</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>18302</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38486</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47067</t>
+          <t>46341</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71353</t>
+          <t>70995</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28939</t>
+          <t>29060</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51378</t>
+          <t>50732</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80188</t>
+          <t>82236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113112</t>
+          <t>114733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -5407,12 +5407,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26384</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47921</t>
+          <t>48850</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21031</t>
+          <t>21083</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40709</t>
+          <t>41399</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52593</t>
+          <t>52459</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82205</t>
+          <t>81742</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -5751,32 +5751,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>265903</t>
+          <t>26533</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73724</t>
+          <t>18054</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>317149</t>
+          <t>35414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5786,32 +5786,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12564</t>
+          <t>13864</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24088</t>
+          <t>26262</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5821,32 +5821,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>283751</t>
+          <t>46137</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89979</t>
+          <t>35695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>371501</t>
+          <t>57854</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -5864,32 +5864,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>304199</t>
+          <t>61529</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215045</t>
+          <t>52194</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>327070</t>
+          <t>70644</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5899,32 +5899,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52062</t>
+          <t>55338</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45972</t>
+          <t>48769</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57547</t>
+          <t>61219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5934,32 +5934,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>356261</t>
+          <t>116866</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>274642</t>
+          <t>104218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>392605</t>
+          <t>127202</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -5977,32 +5977,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>256815</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36677</t>
+          <t>7316</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>314865</t>
+          <t>21982</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6012,32 +6012,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>13156</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6047,32 +6047,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>263668</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>366736</t>
+          <t>30476</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6090,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6160,32 +6160,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>431</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -6207,32 +6207,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>76236</t>
+          <t>80660</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64582</t>
+          <t>66843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89489</t>
+          <t>93045</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6242,32 +6242,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>49882</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37876</t>
+          <t>40477</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54064</t>
+          <t>60265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6277,32 +6277,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>121602</t>
+          <t>130542</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107199</t>
+          <t>114589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>136280</t>
+          <t>146924</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -6320,32 +6320,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>118353</t>
+          <t>124803</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>105102</t>
+          <t>112389</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>130251</t>
+          <t>138198</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6355,32 +6355,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>121375</t>
+          <t>135264</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>112916</t>
+          <t>125957</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>128560</t>
+          <t>143303</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6390,32 +6390,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>239728</t>
+          <t>260067</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>225026</t>
+          <t>244269</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>253716</t>
+          <t>275967</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,96%</t>
         </is>
       </c>
     </row>
@@ -6433,32 +6433,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26583</t>
+          <t>26909</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19178</t>
+          <t>18763</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37268</t>
+          <t>36910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6468,32 +6468,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>17828</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20511</t>
+          <t>26002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6503,32 +6503,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>41532</t>
+          <t>44738</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31630</t>
+          <t>34725</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>56446</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -6663,32 +6663,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>75311</t>
+          <t>82329</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64426</t>
+          <t>71397</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85220</t>
+          <t>94040</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6698,32 +6698,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51471</t>
+          <t>56780</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43670</t>
+          <t>48218</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59996</t>
+          <t>65751</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6733,32 +6733,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>126782</t>
+          <t>139110</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112863</t>
+          <t>124768</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>139625</t>
+          <t>153826</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -6776,32 +6776,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>102501</t>
+          <t>110413</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92267</t>
+          <t>99162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112278</t>
+          <t>120942</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6811,32 +6811,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>102421</t>
+          <t>113242</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95137</t>
+          <t>104951</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109511</t>
+          <t>121395</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6846,32 +6846,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>204922</t>
+          <t>223656</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192059</t>
+          <t>210073</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217473</t>
+          <t>236057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -6889,32 +6889,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22515</t>
+          <t>24627</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31495</t>
+          <t>33410</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6924,32 +6924,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>20670</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24086</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6959,32 +6959,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>40422</t>
+          <t>45297</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32299</t>
+          <t>34990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50819</t>
+          <t>56087</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -7002,32 +7002,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>375</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7072,32 +7072,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>911</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>52979</t>
+          <t>57882</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44760</t>
+          <t>50013</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59810</t>
+          <t>65553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59618</t>
+          <t>65917</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52134</t>
+          <t>57623</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66690</t>
+          <t>73695</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>112598</t>
+          <t>123799</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102595</t>
+          <t>112182</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124308</t>
+          <t>135760</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,58%</t>
         </is>
       </c>
     </row>
@@ -7232,32 +7232,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63992</t>
+          <t>69498</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55886</t>
+          <t>61716</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70855</t>
+          <t>77399</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7267,32 +7267,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>62149</t>
+          <t>69058</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54157</t>
+          <t>60892</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69110</t>
+          <t>76986</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7302,32 +7302,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>126142</t>
+          <t>138556</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115604</t>
+          <t>126051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>137156</t>
+          <t>150443</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,13%</t>
         </is>
       </c>
     </row>
@@ -7345,32 +7345,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15424</t>
+          <t>17394</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7380,32 +7380,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14215</t>
+          <t>15859</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9704</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7415,32 +7415,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>26998</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17384</t>
+          <t>19930</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31581</t>
+          <t>36182</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>660</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>660</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>470429</t>
+          <t>247403</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>324645</t>
+          <t>224008</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>638546</t>
+          <t>268391</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>174304</t>
+          <t>192185</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>159143</t>
+          <t>176466</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>189444</t>
+          <t>209550</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>644732</t>
+          <t>439588</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>488561</t>
+          <t>413953</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>939193</t>
+          <t>465238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -7688,32 +7688,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>589045</t>
+          <t>366242</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>491588</t>
+          <t>344945</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>699871</t>
+          <t>388744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7723,32 +7723,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>338007</t>
+          <t>372902</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>323663</t>
+          <t>356019</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>351987</t>
+          <t>388187</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7758,32 +7758,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>927052</t>
+          <t>739144</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>840970</t>
+          <t>713361</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1087759</t>
+          <t>763640</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>69,48%</t>
         </is>
       </c>
     </row>
@@ -7801,32 +7801,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>315969</t>
+          <t>76147</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>96806</t>
+          <t>61756</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>574811</t>
+          <t>94022</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7836,32 +7836,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>53924</t>
+          <t>62077</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44454</t>
+          <t>51114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64367</t>
+          <t>73872</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7871,32 +7871,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>369892</t>
+          <t>138224</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>148812</t>
+          <t>120008</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>786892</t>
+          <t>155990</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -7914,32 +7914,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7949,22 +7949,22 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7984,32 +7984,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
